--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/94.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/94.xlsx
@@ -426,13 +426,13 @@
         <v>-16.14455205427583</v>
       </c>
       <c r="E2">
-        <v>-11.45481330690183</v>
+        <v>-9.738743553221143</v>
       </c>
       <c r="F2">
-        <v>-3.020753711155283</v>
+        <v>-2.882691372865495</v>
       </c>
       <c r="G2">
-        <v>-9.394776530014905</v>
+        <v>-8.443107246022773</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.99561958914642</v>
       </c>
       <c r="E3">
-        <v>-12.25721814479495</v>
+        <v>-10.68241413778354</v>
       </c>
       <c r="F3">
-        <v>-2.626705964582781</v>
+        <v>-3.132677744417135</v>
       </c>
       <c r="G3">
-        <v>-9.236595353602988</v>
+        <v>-8.179978465470422</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.90698932473537</v>
       </c>
       <c r="E4">
-        <v>-12.35062697815117</v>
+        <v>-11.30956250310581</v>
       </c>
       <c r="F4">
-        <v>-2.617275830069311</v>
+        <v>-2.987445886256118</v>
       </c>
       <c r="G4">
-        <v>-8.911443502372389</v>
+        <v>-8.399957595463913</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.9095264599738</v>
       </c>
       <c r="E5">
-        <v>-12.70005761800503</v>
+        <v>-12.40289009667369</v>
       </c>
       <c r="F5">
-        <v>-2.362402090841154</v>
+        <v>-3.030557439367415</v>
       </c>
       <c r="G5">
-        <v>-8.914485893722979</v>
+        <v>-8.992780295726744</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.97122633655865</v>
       </c>
       <c r="E6">
-        <v>-13.62567317669885</v>
+        <v>-12.09008575459386</v>
       </c>
       <c r="F6">
-        <v>-2.289080806917161</v>
+        <v>-2.764764989402957</v>
       </c>
       <c r="G6">
-        <v>-8.884704226051696</v>
+        <v>-7.950829124333148</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.09314823390089</v>
       </c>
       <c r="E7">
-        <v>-14.47755612159977</v>
+        <v>-12.75392834480028</v>
       </c>
       <c r="F7">
-        <v>-2.087853797429105</v>
+        <v>-2.918780855503261</v>
       </c>
       <c r="G7">
-        <v>-8.600765356239485</v>
+        <v>-8.043934907079612</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.23943242192291</v>
       </c>
       <c r="E8">
-        <v>-15.04711135449249</v>
+        <v>-13.15001585235518</v>
       </c>
       <c r="F8">
-        <v>-2.263608509281076</v>
+        <v>-2.650597737214324</v>
       </c>
       <c r="G8">
-        <v>-8.371966932929375</v>
+        <v>-8.335140424350522</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.39501606475241</v>
       </c>
       <c r="E9">
-        <v>-15.98468661304056</v>
+        <v>-14.46597228508815</v>
       </c>
       <c r="F9">
-        <v>-2.304184429772404</v>
+        <v>-2.310090689354364</v>
       </c>
       <c r="G9">
-        <v>-8.15263998040712</v>
+        <v>-7.783060608039502</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.53019572647978</v>
       </c>
       <c r="E10">
-        <v>-16.33908951735485</v>
+        <v>-16.07858905006361</v>
       </c>
       <c r="F10">
-        <v>-2.037515567095785</v>
+        <v>-2.427574724623808</v>
       </c>
       <c r="G10">
-        <v>-7.791432977708319</v>
+        <v>-7.627829127703076</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.620497627546</v>
       </c>
       <c r="E11">
-        <v>-17.3101890689817</v>
+        <v>-15.43778733560822</v>
       </c>
       <c r="F11">
-        <v>-1.63558756142045</v>
+        <v>-2.06273935451103</v>
       </c>
       <c r="G11">
-        <v>-7.614355207358242</v>
+        <v>-7.274391975384945</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.65561472796804</v>
       </c>
       <c r="E12">
-        <v>-17.89794423891125</v>
+        <v>-16.06832752796223</v>
       </c>
       <c r="F12">
-        <v>-1.422649921959018</v>
+        <v>-1.785084683338483</v>
       </c>
       <c r="G12">
-        <v>-7.820383698449246</v>
+        <v>-6.459686581443541</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.61604168037828</v>
       </c>
       <c r="E13">
-        <v>-19.25044545688612</v>
+        <v>-16.51822236367627</v>
       </c>
       <c r="F13">
-        <v>-1.320893270199127</v>
+        <v>-1.942075216782239</v>
       </c>
       <c r="G13">
-        <v>-6.511920368962162</v>
+        <v>-6.16289286330234</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.52227559300831</v>
       </c>
       <c r="E14">
-        <v>-19.80010710346314</v>
+        <v>-17.38822373308188</v>
       </c>
       <c r="F14">
-        <v>-1.474298629523567</v>
+        <v>-1.57747013280744</v>
       </c>
       <c r="G14">
-        <v>-6.97670440994814</v>
+        <v>-5.916906087552333</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.3732702952607</v>
       </c>
       <c r="E15">
-        <v>-20.55374027629365</v>
+        <v>-18.84747919731358</v>
       </c>
       <c r="F15">
-        <v>-0.986771278279946</v>
+        <v>-1.492150775421299</v>
       </c>
       <c r="G15">
-        <v>-5.930029090070005</v>
+        <v>-6.102356227571227</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.20805136366589</v>
       </c>
       <c r="E16">
-        <v>-20.73176364648319</v>
+        <v>-19.02930195719555</v>
       </c>
       <c r="F16">
-        <v>-0.8182564975284427</v>
+        <v>-1.017132600327354</v>
       </c>
       <c r="G16">
-        <v>-6.541437192990304</v>
+        <v>-5.445534060943205</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.03084845587118</v>
       </c>
       <c r="E17">
-        <v>-22.58555335168515</v>
+        <v>-20.69981073388507</v>
       </c>
       <c r="F17">
-        <v>-0.3120825960478047</v>
+        <v>-0.8577389730480754</v>
       </c>
       <c r="G17">
-        <v>-6.519574350248957</v>
+        <v>-5.763568239264371</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.87775409417497</v>
       </c>
       <c r="E18">
-        <v>-23.05916380577735</v>
+        <v>-20.99037574011323</v>
       </c>
       <c r="F18">
-        <v>-0.3054589702950198</v>
+        <v>-0.500483164670913</v>
       </c>
       <c r="G18">
-        <v>-6.42757760025815</v>
+        <v>-5.314466252497921</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.7428190998343</v>
       </c>
       <c r="E19">
-        <v>-23.71288072810262</v>
+        <v>-21.73391494438064</v>
       </c>
       <c r="F19">
-        <v>0.2593285518729055</v>
+        <v>-0.02752928114474372</v>
       </c>
       <c r="G19">
-        <v>-6.441342848610439</v>
+        <v>-5.321047617029992</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.64860961427397</v>
       </c>
       <c r="E20">
-        <v>-24.26206235643483</v>
+        <v>-22.95428887623371</v>
       </c>
       <c r="F20">
-        <v>0.6670360769175717</v>
+        <v>0.3909884385064561</v>
       </c>
       <c r="G20">
-        <v>-6.228974662811733</v>
+        <v>-5.63529784179977</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-15.57878350686608</v>
       </c>
       <c r="E21">
-        <v>-24.85011640564888</v>
+        <v>-22.90420395370888</v>
       </c>
       <c r="F21">
-        <v>0.8742463841560485</v>
+        <v>0.4587853402211788</v>
       </c>
       <c r="G21">
-        <v>-5.751792628781184</v>
+        <v>-5.690130407566718</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-15.5419228014348</v>
       </c>
       <c r="E22">
-        <v>-25.22082634486479</v>
+        <v>-23.97876102251497</v>
       </c>
       <c r="F22">
-        <v>1.437711831949106</v>
+        <v>0.5632971419627812</v>
       </c>
       <c r="G22">
-        <v>-6.118313057070514</v>
+        <v>-5.628706545631081</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-15.52022196200795</v>
       </c>
       <c r="E23">
-        <v>-26.19196212428371</v>
+        <v>-22.90959283777801</v>
       </c>
       <c r="F23">
-        <v>1.655656952360461</v>
+        <v>1.008200020127951</v>
       </c>
       <c r="G23">
-        <v>-6.783894927195447</v>
+        <v>-6.105524419652309</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-15.50901822435217</v>
       </c>
       <c r="E24">
-        <v>-26.1768415495721</v>
+        <v>-24.10038224893897</v>
       </c>
       <c r="F24">
-        <v>1.67375678011163</v>
+        <v>1.240394716602264</v>
       </c>
       <c r="G24">
-        <v>-6.381435216531788</v>
+        <v>-5.940513587792877</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-15.49809254909323</v>
       </c>
       <c r="E25">
-        <v>-26.5035664207515</v>
+        <v>-24.88162552779425</v>
       </c>
       <c r="F25">
-        <v>1.724227549229399</v>
+        <v>1.472887625341584</v>
       </c>
       <c r="G25">
-        <v>-6.853178024241315</v>
+        <v>-5.417569882772982</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-15.47050229630934</v>
       </c>
       <c r="E26">
-        <v>-27.27569388142934</v>
+        <v>-23.90425403966677</v>
       </c>
       <c r="F26">
-        <v>1.90381428868672</v>
+        <v>1.346246816801596</v>
       </c>
       <c r="G26">
-        <v>-7.63780049086736</v>
+        <v>-6.378101497173742</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-15.42482161862683</v>
       </c>
       <c r="E27">
-        <v>-27.85734466839654</v>
+        <v>-23.73101273802934</v>
       </c>
       <c r="F27">
-        <v>1.768609817936591</v>
+        <v>1.699272152852661</v>
       </c>
       <c r="G27">
-        <v>-6.805489615748114</v>
+        <v>-6.120944940774235</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.33725774384245</v>
       </c>
       <c r="E28">
-        <v>-26.38598006466833</v>
+        <v>-23.786903164232</v>
       </c>
       <c r="F28">
-        <v>2.052657000356541</v>
+        <v>1.472521486949547</v>
       </c>
       <c r="G28">
-        <v>-7.507682808991846</v>
+        <v>-6.610147565657877</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-15.21485093637878</v>
       </c>
       <c r="E29">
-        <v>-25.90698978345502</v>
+        <v>-24.52704148451965</v>
       </c>
       <c r="F29">
-        <v>1.894327825189861</v>
+        <v>1.889258216684728</v>
       </c>
       <c r="G29">
-        <v>-7.119458444147053</v>
+        <v>-6.008939253544073</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-15.03528802541796</v>
       </c>
       <c r="E30">
-        <v>-26.06766909819518</v>
+        <v>-24.17747951891957</v>
       </c>
       <c r="F30">
-        <v>1.970043919275347</v>
+        <v>1.486336998493437</v>
       </c>
       <c r="G30">
-        <v>-7.394796516648237</v>
+        <v>-6.332293478546847</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.81136007319263</v>
       </c>
       <c r="E31">
-        <v>-26.38107119884402</v>
+        <v>-23.8578643519322</v>
       </c>
       <c r="F31">
-        <v>1.851307392492871</v>
+        <v>1.775104218374539</v>
       </c>
       <c r="G31">
-        <v>-6.997339040294418</v>
+        <v>-6.471008647187849</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-14.5300801329911</v>
       </c>
       <c r="E32">
-        <v>-25.64562437762832</v>
+        <v>-23.8935849549047</v>
       </c>
       <c r="F32">
-        <v>1.654440909013152</v>
+        <v>1.368403988091677</v>
       </c>
       <c r="G32">
-        <v>-6.225101324530785</v>
+        <v>-6.171732019892194</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-14.21264496526873</v>
       </c>
       <c r="E33">
-        <v>-24.63482369437622</v>
+        <v>-22.96734899527184</v>
       </c>
       <c r="F33">
-        <v>1.172001390357525</v>
+        <v>1.136209291617364</v>
       </c>
       <c r="G33">
-        <v>-6.284386574048053</v>
+        <v>-5.552358744404408</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.85312883824375</v>
       </c>
       <c r="E34">
-        <v>-24.62183150244821</v>
+        <v>-23.00225447292296</v>
       </c>
       <c r="F34">
-        <v>1.698370889118415</v>
+        <v>1.321425615944111</v>
       </c>
       <c r="G34">
-        <v>-6.346714214915912</v>
+        <v>-5.571261959433647</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.47498593237349</v>
       </c>
       <c r="E35">
-        <v>-24.20303369774485</v>
+        <v>-21.95742683597722</v>
       </c>
       <c r="F35">
-        <v>1.697840733980623</v>
+        <v>1.436567028198437</v>
       </c>
       <c r="G35">
-        <v>-7.372447023712618</v>
+        <v>-5.483555676461735</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.07867902789454</v>
       </c>
       <c r="E36">
-        <v>-23.95700170490812</v>
+        <v>-20.89362036446534</v>
       </c>
       <c r="F36">
-        <v>1.512127389212196</v>
+        <v>0.9342119004447047</v>
       </c>
       <c r="G36">
-        <v>-6.264755039000176</v>
+        <v>-5.580091184386883</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.68389940468414</v>
       </c>
       <c r="E37">
-        <v>-23.14724715370055</v>
+        <v>-20.75871259530284</v>
       </c>
       <c r="F37">
-        <v>1.417546055895355</v>
+        <v>1.022749465190721</v>
       </c>
       <c r="G37">
-        <v>-5.719610815593928</v>
+        <v>-4.925583089090813</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.29688644462745</v>
       </c>
       <c r="E38">
-        <v>-23.05509723611847</v>
+        <v>-20.95974514192535</v>
       </c>
       <c r="F38">
-        <v>1.635441474262542</v>
+        <v>0.6932365095007174</v>
       </c>
       <c r="G38">
-        <v>-5.677805246524011</v>
+        <v>-5.105772772247804</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.92676870294138</v>
       </c>
       <c r="E39">
-        <v>-22.56779267662706</v>
+        <v>-20.70015489790965</v>
       </c>
       <c r="F39">
-        <v>1.139229519167971</v>
+        <v>0.7134271365765524</v>
       </c>
       <c r="G39">
-        <v>-5.118263460567474</v>
+        <v>-4.780594436652891</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.58487541155531</v>
       </c>
       <c r="E40">
-        <v>-22.08943185330082</v>
+        <v>-20.07014906548854</v>
       </c>
       <c r="F40">
-        <v>1.472650712264383</v>
+        <v>0.3806065098471699</v>
       </c>
       <c r="G40">
-        <v>-5.161562085675602</v>
+        <v>-4.470505567625978</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.26628650143497</v>
       </c>
       <c r="E41">
-        <v>-21.09229357612986</v>
+        <v>-18.83248541987418</v>
       </c>
       <c r="F41">
-        <v>1.246395410068143</v>
+        <v>0.6781552525653495</v>
       </c>
       <c r="G41">
-        <v>-5.29520549855044</v>
+        <v>-4.053300687130404</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.9795954724478</v>
       </c>
       <c r="E42">
-        <v>-20.44230811638691</v>
+        <v>-19.39691442019021</v>
       </c>
       <c r="F42">
-        <v>0.8857888555466568</v>
+        <v>0.6695435450458459</v>
       </c>
       <c r="G42">
-        <v>-4.735001603486049</v>
+        <v>-4.253850225353914</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.70721909729358</v>
       </c>
       <c r="E43">
-        <v>-20.73341653949599</v>
+        <v>-18.64855239110463</v>
       </c>
       <c r="F43">
-        <v>1.087668618548119</v>
+        <v>0.3590996069682864</v>
       </c>
       <c r="G43">
-        <v>-4.994296772303925</v>
+        <v>-3.980531585631685</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.45723914421497</v>
       </c>
       <c r="E44">
-        <v>-19.44362110110533</v>
+        <v>-18.14496796755566</v>
       </c>
       <c r="F44">
-        <v>0.6874172284960508</v>
+        <v>0.3468778743073824</v>
       </c>
       <c r="G44">
-        <v>-4.622393396967739</v>
+        <v>-3.512989860211493</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.21093905992081</v>
       </c>
       <c r="E45">
-        <v>-19.35468640006869</v>
+        <v>-17.4307415755399</v>
       </c>
       <c r="F45">
-        <v>0.7384007570361519</v>
+        <v>-0.01748449801839692</v>
       </c>
       <c r="G45">
-        <v>-4.704564447797989</v>
+        <v>-3.513764527867683</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.976236663360204</v>
       </c>
       <c r="E46">
-        <v>-19.26797970824382</v>
+        <v>-16.30482708301282</v>
       </c>
       <c r="F46">
-        <v>0.5295063788677838</v>
+        <v>-0.05380426679414124</v>
       </c>
       <c r="G46">
-        <v>-4.665887344262684</v>
+        <v>-3.208919562974974</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.736823209644223</v>
       </c>
       <c r="E47">
-        <v>-18.05287239166167</v>
+        <v>-16.32590712951852</v>
       </c>
       <c r="F47">
-        <v>0.5180467442174554</v>
+        <v>-0.316642758600216</v>
       </c>
       <c r="G47">
-        <v>-4.454628191219633</v>
+        <v>-3.145704695902591</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.498709160323118</v>
       </c>
       <c r="E48">
-        <v>-18.5211256610028</v>
+        <v>-16.11600330231499</v>
       </c>
       <c r="F48">
-        <v>0.2682856885993765</v>
+        <v>0.06977572419250301</v>
       </c>
       <c r="G48">
-        <v>-3.727218572603271</v>
+        <v>-2.405698451509303</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.248497470265592</v>
       </c>
       <c r="E49">
-        <v>-17.1389765236997</v>
+        <v>-15.45202032941433</v>
       </c>
       <c r="F49">
-        <v>0.01448220005563601</v>
+        <v>-0.3424729109543102</v>
       </c>
       <c r="G49">
-        <v>-4.989675250731103</v>
+        <v>-2.904273230814622</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.991660587350422</v>
       </c>
       <c r="E50">
-        <v>-17.39440510010235</v>
+        <v>-15.34550609227991</v>
       </c>
       <c r="F50">
-        <v>-0.09511991937616938</v>
+        <v>-0.4758980485232265</v>
       </c>
       <c r="G50">
-        <v>-4.938815339611279</v>
+        <v>-3.302429232277228</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.722310787272967</v>
       </c>
       <c r="E51">
-        <v>-16.54856766800167</v>
+        <v>-14.63515154554071</v>
       </c>
       <c r="F51">
-        <v>-0.08962204492378907</v>
+        <v>-0.4951310828814254</v>
       </c>
       <c r="G51">
-        <v>-4.757910578617805</v>
+        <v>-3.033503686485612</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.445882305540286</v>
       </c>
       <c r="E52">
-        <v>-15.723402719746</v>
+        <v>-14.3408369628342</v>
       </c>
       <c r="F52">
-        <v>-0.07520265354325807</v>
+        <v>-0.9393331622238268</v>
       </c>
       <c r="G52">
-        <v>-4.943132290994489</v>
+        <v>-2.68088423891568</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.164623212092151</v>
       </c>
       <c r="E53">
-        <v>-15.11012959878323</v>
+        <v>-14.10625748076287</v>
       </c>
       <c r="F53">
-        <v>-0.3377197387970466</v>
+        <v>-0.7074101702576323</v>
       </c>
       <c r="G53">
-        <v>-4.659325843003849</v>
+        <v>-3.028802711819846</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.879666984172969</v>
       </c>
       <c r="E54">
-        <v>-15.22167949901417</v>
+        <v>-13.92823863904734</v>
       </c>
       <c r="F54">
-        <v>-0.3621516069752152</v>
+        <v>-0.7166704894535281</v>
       </c>
       <c r="G54">
-        <v>-4.852714671225915</v>
+        <v>-3.684264244231227</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.599306647890962</v>
       </c>
       <c r="E55">
-        <v>-15.12694835124772</v>
+        <v>-13.28931171283112</v>
       </c>
       <c r="F55">
-        <v>-0.2095456221944763</v>
+        <v>-0.4176099762252393</v>
       </c>
       <c r="G55">
-        <v>-4.845484439768146</v>
+        <v>-3.283810724164367</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.318432999560141</v>
       </c>
       <c r="E56">
-        <v>-13.94598120020939</v>
+        <v>-13.22615308584614</v>
       </c>
       <c r="F56">
-        <v>-0.5589948961676562</v>
+        <v>-0.7385360754178237</v>
       </c>
       <c r="G56">
-        <v>-5.4143089954168</v>
+        <v>-3.307729415685601</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.049218759686032</v>
       </c>
       <c r="E57">
-        <v>-13.30298317586027</v>
+        <v>-12.80233773194228</v>
       </c>
       <c r="F57">
-        <v>-0.4951998373758578</v>
+        <v>-0.8292795825574957</v>
       </c>
       <c r="G57">
-        <v>-5.085601618277025</v>
+        <v>-3.330956203189128</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.783948598268861</v>
       </c>
       <c r="E58">
-        <v>-13.90894281130065</v>
+        <v>-11.3695421413374</v>
       </c>
       <c r="F58">
-        <v>0.05425460416624867</v>
+        <v>-1.064046359817501</v>
       </c>
       <c r="G58">
-        <v>-5.625842923739611</v>
+        <v>-3.871313377745589</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.532490402955284</v>
       </c>
       <c r="E59">
-        <v>-13.36201183455026</v>
+        <v>-11.50056447980133</v>
       </c>
       <c r="F59">
-        <v>-0.4733450201877984</v>
+        <v>-0.8511286011737353</v>
       </c>
       <c r="G59">
-        <v>-5.559880303869632</v>
+        <v>-4.065635779809729</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.287721901541164</v>
       </c>
       <c r="E60">
-        <v>-12.96739608104786</v>
+        <v>-11.42447705952445</v>
       </c>
       <c r="F60">
-        <v>-0.3543177364469403</v>
+        <v>-0.7581832934774224</v>
       </c>
       <c r="G60">
-        <v>-5.513843857600527</v>
+        <v>-3.391986110205592</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.056714341487973</v>
       </c>
       <c r="E61">
-        <v>-13.0034382056749</v>
+        <v>-11.52866818949293</v>
       </c>
       <c r="F61">
-        <v>-0.6953648798535248</v>
+        <v>-0.8810707693153264</v>
       </c>
       <c r="G61">
-        <v>-5.753431348823122</v>
+        <v>-3.76124767020144</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.832600387180899</v>
       </c>
       <c r="E62">
-        <v>-13.03064074903898</v>
+        <v>-11.22028816651859</v>
       </c>
       <c r="F62">
-        <v>-0.6744254086455589</v>
+        <v>-0.8877788885431968</v>
       </c>
       <c r="G62">
-        <v>-6.041918908206292</v>
+        <v>-4.020188610646614</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.621864152002371</v>
       </c>
       <c r="E63">
-        <v>-11.85452359366287</v>
+        <v>-11.8642281134613</v>
       </c>
       <c r="F63">
-        <v>-0.7510253707498319</v>
+        <v>-0.8901041158428549</v>
       </c>
       <c r="G63">
-        <v>-5.786175954752053</v>
+        <v>-3.728234910083827</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.418979814743976</v>
       </c>
       <c r="E64">
-        <v>-11.09911525902135</v>
+        <v>-11.31173164215548</v>
       </c>
       <c r="F64">
-        <v>-0.8590461368096931</v>
+        <v>-0.9409468219244802</v>
       </c>
       <c r="G64">
-        <v>-6.07822235058994</v>
+        <v>-4.265010074366796</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.227816633696668</v>
       </c>
       <c r="E65">
-        <v>-11.82483491806858</v>
+        <v>-11.39815304011786</v>
       </c>
       <c r="F65">
-        <v>-1.210080077624428</v>
+        <v>-1.066403065078465</v>
       </c>
       <c r="G65">
-        <v>-6.144516025013846</v>
+        <v>-3.91250980643628</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.044954626724975</v>
       </c>
       <c r="E66">
-        <v>-11.86229445506003</v>
+        <v>-10.83574826768326</v>
       </c>
       <c r="F66">
-        <v>-0.8991855076797459</v>
+        <v>-1.230037933460077</v>
       </c>
       <c r="G66">
-        <v>-5.642104323428511</v>
+        <v>-3.785785433738518</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.871188623499556</v>
       </c>
       <c r="E67">
-        <v>-11.44901233169801</v>
+        <v>-11.1451970105234</v>
       </c>
       <c r="F67">
-        <v>-0.9148880401672134</v>
+        <v>-1.302156427915205</v>
       </c>
       <c r="G67">
-        <v>-5.79945786345561</v>
+        <v>-3.612233394387765</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.707029207618109</v>
       </c>
       <c r="E68">
-        <v>-11.20491852573656</v>
+        <v>-10.7394230970661</v>
       </c>
       <c r="F68">
-        <v>-1.305869998981955</v>
+        <v>-1.618997019077182</v>
       </c>
       <c r="G68">
-        <v>-5.650191986180951</v>
+        <v>-3.334227022181928</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.550246877011876</v>
       </c>
       <c r="E69">
-        <v>-10.92456522839569</v>
+        <v>-11.14088137479409</v>
       </c>
       <c r="F69">
-        <v>-1.171653770543365</v>
+        <v>-1.487581500827457</v>
       </c>
       <c r="G69">
-        <v>-5.241124426620907</v>
+        <v>-3.682224948179036</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.405333442686486</v>
       </c>
       <c r="E70">
-        <v>-11.67592057880035</v>
+        <v>-10.48970945486113</v>
       </c>
       <c r="F70">
-        <v>-1.170734282726257</v>
+        <v>-1.416076826617804</v>
       </c>
       <c r="G70">
-        <v>-5.338156516376945</v>
+        <v>-3.478990557523178</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.267662667425784</v>
       </c>
       <c r="E71">
-        <v>-11.43964744745015</v>
+        <v>-11.34147465943786</v>
       </c>
       <c r="F71">
-        <v>-1.090502757928111</v>
+        <v>-1.498767774234862</v>
       </c>
       <c r="G71">
-        <v>-4.949816282438277</v>
+        <v>-3.253413295022779</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.143660034437629</v>
       </c>
       <c r="E72">
-        <v>-11.76020906550511</v>
+        <v>-11.50654659396546</v>
       </c>
       <c r="F72">
-        <v>-1.239979170661074</v>
+        <v>-1.384387631623709</v>
       </c>
       <c r="G72">
-        <v>-5.094450706503497</v>
+        <v>-3.643259827181815</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.027539910434462</v>
       </c>
       <c r="E73">
-        <v>-11.78577682975242</v>
+        <v>-11.32888097322253</v>
       </c>
       <c r="F73">
-        <v>-1.138367483196672</v>
+        <v>-1.630623155575473</v>
       </c>
       <c r="G73">
-        <v>-4.38895689935711</v>
+        <v>-3.387295067176445</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.923981245650796</v>
       </c>
       <c r="E74">
-        <v>-12.89253587722706</v>
+        <v>-11.92395868562247</v>
       </c>
       <c r="F74">
-        <v>-1.301342971125655</v>
+        <v>-1.923276246943108</v>
       </c>
       <c r="G74">
-        <v>-4.17937288235693</v>
+        <v>-3.464735348431077</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.826738170648058</v>
       </c>
       <c r="E75">
-        <v>-12.20569316753568</v>
+        <v>-11.47802173619114</v>
       </c>
       <c r="F75">
-        <v>-1.518484575156295</v>
+        <v>-1.991715961762403</v>
       </c>
       <c r="G75">
-        <v>-4.055257219544114</v>
+        <v>-2.879361375631606</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.739270847481112</v>
       </c>
       <c r="E76">
-        <v>-12.60750466623627</v>
+        <v>-12.40182137680788</v>
       </c>
       <c r="F76">
-        <v>-1.738033414859471</v>
+        <v>-1.998965833271704</v>
       </c>
       <c r="G76">
-        <v>-3.943148905402234</v>
+        <v>-3.466165504104042</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.655940447001194</v>
       </c>
       <c r="E77">
-        <v>-12.51562645709464</v>
+        <v>-11.95804903795222</v>
       </c>
       <c r="F77">
-        <v>-1.606629493753385</v>
+        <v>-2.14888128072815</v>
       </c>
       <c r="G77">
-        <v>-3.751819236505595</v>
+        <v>-2.648629593726561</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.58062769724692</v>
       </c>
       <c r="E78">
-        <v>-13.37932871915559</v>
+        <v>-13.29172991795121</v>
       </c>
       <c r="F78">
-        <v>-1.829566356134011</v>
+        <v>-2.070454768500704</v>
       </c>
       <c r="G78">
-        <v>-3.432219170144355</v>
+        <v>-2.147326924896883</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.510923176042263</v>
       </c>
       <c r="E79">
-        <v>-13.90535625988658</v>
+        <v>-13.25726823075284</v>
       </c>
       <c r="F79">
-        <v>-1.699062870394768</v>
+        <v>-2.206053542134566</v>
       </c>
       <c r="G79">
-        <v>-3.158480091138638</v>
+        <v>-1.499211493037145</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.454288371889492</v>
       </c>
       <c r="E80">
-        <v>-14.38352688730451</v>
+        <v>-14.08341132939417</v>
       </c>
       <c r="F80">
-        <v>-1.805394595320321</v>
+        <v>-2.287294846796725</v>
       </c>
       <c r="G80">
-        <v>-3.015898205307768</v>
+        <v>-1.905124102698263</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.412245924364392</v>
       </c>
       <c r="E81">
-        <v>-14.89836004028853</v>
+        <v>-14.76864190233882</v>
       </c>
       <c r="F81">
-        <v>-1.919440905868146</v>
+        <v>-2.223273643703962</v>
       </c>
       <c r="G81">
-        <v>-2.575353978760333</v>
+        <v>-1.307537527404421</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.393241367082098</v>
       </c>
       <c r="E82">
-        <v>-15.94444206453439</v>
+        <v>-15.55206337719178</v>
       </c>
       <c r="F82">
-        <v>-2.060919431327079</v>
+        <v>-2.721279014225594</v>
       </c>
       <c r="G82">
-        <v>-2.498489732429535</v>
+        <v>-1.473650770928432</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.404081345594146</v>
       </c>
       <c r="E83">
-        <v>-16.25816568683778</v>
+        <v>-15.82364954885379</v>
       </c>
       <c r="F83">
-        <v>-2.107356051193213</v>
+        <v>-2.647859982948071</v>
       </c>
       <c r="G83">
-        <v>-1.769484430863244</v>
+        <v>-0.7170123457458447</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.451619691220853</v>
       </c>
       <c r="E84">
-        <v>-17.5608627476763</v>
+        <v>-17.10267627605422</v>
       </c>
       <c r="F84">
-        <v>-2.159946612494746</v>
+        <v>-2.899853488716695</v>
       </c>
       <c r="G84">
-        <v>-1.742708738541619</v>
+        <v>-0.8586010679149341</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.546114457320906</v>
       </c>
       <c r="E85">
-        <v>-18.0892586803133</v>
+        <v>-17.68359797870619</v>
       </c>
       <c r="F85">
-        <v>-2.229715856995534</v>
+        <v>-3.061338743688042</v>
       </c>
       <c r="G85">
-        <v>-1.225197638751668</v>
+        <v>-0.740931037267079</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.691078329580218</v>
       </c>
       <c r="E86">
-        <v>-19.77686697485578</v>
+        <v>-19.20067299906782</v>
       </c>
       <c r="F86">
-        <v>-2.569399507657111</v>
+        <v>-3.104579522114176</v>
       </c>
       <c r="G86">
-        <v>-1.311189059134237</v>
+        <v>0.08528181296883114</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.89713248891311</v>
       </c>
       <c r="E87">
-        <v>-21.06418080949024</v>
+        <v>-19.335390572322</v>
       </c>
       <c r="F87">
-        <v>-2.705922739312497</v>
+        <v>-2.860187115633641</v>
       </c>
       <c r="G87">
-        <v>-1.811902450857926</v>
+        <v>-0.6931466229532387</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.162813180960292</v>
       </c>
       <c r="E88">
-        <v>-22.59356875067873</v>
+        <v>-21.6409091452111</v>
       </c>
       <c r="F88">
-        <v>-2.455006939534916</v>
+        <v>-3.246256027382378</v>
       </c>
       <c r="G88">
-        <v>-1.477567146301389</v>
+        <v>-0.4461997889968438</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.498234404611227</v>
       </c>
       <c r="E89">
-        <v>-22.91568363531833</v>
+        <v>-22.61785495678186</v>
       </c>
       <c r="F89">
-        <v>-2.670531570395291</v>
+        <v>-3.584932383282151</v>
       </c>
       <c r="G89">
-        <v>-1.575976423001765</v>
+        <v>-0.04456771471800263</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.897570530491324</v>
       </c>
       <c r="E90">
-        <v>-25.30456688621463</v>
+        <v>-24.05921842020925</v>
       </c>
       <c r="F90">
-        <v>-3.138414188681522</v>
+        <v>-3.200108507739821</v>
       </c>
       <c r="G90">
-        <v>-1.414564154143519</v>
+        <v>-0.2201557395754071</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.371325218152218</v>
       </c>
       <c r="E91">
-        <v>-26.10164171020072</v>
+        <v>-26.23610568891048</v>
       </c>
       <c r="F91">
-        <v>-3.066363620353424</v>
+        <v>-3.585909028450051</v>
       </c>
       <c r="G91">
-        <v>-1.829395373487435</v>
+        <v>-0.6139087154707829</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.908501746465914</v>
       </c>
       <c r="E92">
-        <v>-28.03304945989415</v>
+        <v>-26.9322453557396</v>
       </c>
       <c r="F92">
-        <v>-2.911823397687148</v>
+        <v>-3.499328067509447</v>
       </c>
       <c r="G92">
-        <v>-1.566941944225094</v>
+        <v>-0.4926070163663473</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.518687749601113</v>
       </c>
       <c r="E93">
-        <v>-29.78634100568089</v>
+        <v>-29.46942480920209</v>
       </c>
       <c r="F93">
-        <v>-2.703939627750195</v>
+        <v>-3.775914144732382</v>
       </c>
       <c r="G93">
-        <v>-2.082086003954465</v>
+        <v>-1.254717773325349</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.18557584273838</v>
       </c>
       <c r="E94">
-        <v>-32.17430950482765</v>
+        <v>-30.72960176334559</v>
       </c>
       <c r="F94">
-        <v>-2.641275290463218</v>
+        <v>-3.899497449188638</v>
       </c>
       <c r="G94">
-        <v>-2.760002966758722</v>
+        <v>-1.653916596632826</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.910934747748934</v>
       </c>
       <c r="E95">
-        <v>-34.24430893728882</v>
+        <v>-33.2205658753228</v>
       </c>
       <c r="F95">
-        <v>-2.759244749030701</v>
+        <v>-4.189757387129585</v>
       </c>
       <c r="G95">
-        <v>-2.824167960400877</v>
+        <v>-1.993843412605192</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.685114176842436</v>
       </c>
       <c r="E96">
-        <v>-36.44154716818052</v>
+        <v>-36.23813037999297</v>
       </c>
       <c r="F96">
-        <v>-3.030765359585518</v>
+        <v>-3.796113883849648</v>
       </c>
       <c r="G96">
-        <v>-3.232917707589151</v>
+        <v>-2.628223391022494</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.492368899573561</v>
       </c>
       <c r="E97">
-        <v>-38.79942848602031</v>
+        <v>-37.57146936020439</v>
       </c>
       <c r="F97">
-        <v>-2.775122895407562</v>
+        <v>-3.906571706808545</v>
       </c>
       <c r="G97">
-        <v>-4.101730657824403</v>
+        <v>-2.268072452350721</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.34353960712565</v>
       </c>
       <c r="E98">
-        <v>-40.63349668691887</v>
+        <v>-40.19264747803516</v>
       </c>
       <c r="F98">
-        <v>-2.653682577422349</v>
+        <v>-3.870555948869629</v>
       </c>
       <c r="G98">
-        <v>-4.212653796663223</v>
+        <v>-3.329684953702048</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.19742413063048</v>
       </c>
       <c r="E99">
-        <v>-43.64168498615616</v>
+        <v>-42.4764678677165</v>
       </c>
       <c r="F99">
-        <v>-2.575367894794281</v>
+        <v>-4.209304372733444</v>
       </c>
       <c r="G99">
-        <v>-4.776396664909096</v>
+        <v>-3.826958688610433</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.1054745413553</v>
       </c>
       <c r="E100">
-        <v>-45.35927404286642</v>
+        <v>-44.8345280602796</v>
       </c>
       <c r="F100">
-        <v>-2.803020652799044</v>
+        <v>-4.151897683352036</v>
       </c>
       <c r="G100">
-        <v>-5.015649791032224</v>
+        <v>-4.102117991652498</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.97479114754151</v>
       </c>
       <c r="E101">
-        <v>-47.85670255148958</v>
+        <v>-46.16651755523673</v>
       </c>
       <c r="F101">
-        <v>-2.739276952786219</v>
+        <v>-4.393500976787346</v>
       </c>
       <c r="G101">
-        <v>-5.587271757661562</v>
+        <v>-5.073951808524329</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.95427359418113</v>
       </c>
       <c r="E102">
-        <v>-49.60569204696903</v>
+        <v>-48.80421214989197</v>
       </c>
       <c r="F102">
-        <v>-2.718036784211037</v>
+        <v>-4.213818975078702</v>
       </c>
       <c r="G102">
-        <v>-6.335647061178128</v>
+        <v>-4.988145778691959</v>
       </c>
     </row>
   </sheetData>
